--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05CFCC7-41A8-44AB-B84E-AE99E4B6E141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06259BE4-5400-4C55-BB30-36C11C515CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Autor</author>
+    <author>Author</author>
   </authors>
   <commentList>
     <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
@@ -46,7 +46,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Autor:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Autor</author>
+    <author>Author</author>
   </authors>
   <commentList>
     <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
@@ -81,7 +81,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Autor:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -105,7 +105,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Autor:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
   <si>
     <t>Condition</t>
   </si>
@@ -350,9 +350,6 @@
   </si>
   <si>
     <t>"Cola"</t>
-  </si>
-  <si>
-    <t>SOFT_DRINK</t>
   </si>
   <si>
     <t>valid</t>
@@ -454,12 +451,27 @@
   <si>
     <t>TC1_BVA</t>
   </si>
+  <si>
+    <t>Bontidean Alexandra-Mihaela</t>
+  </si>
+  <si>
+    <t>TC5_ECP</t>
+  </si>
+  <si>
+    <t>TC2_BVA</t>
+  </si>
+  <si>
+    <t>TC3_BVA</t>
+  </si>
+  <si>
+    <t>TC4_BVA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,15 +538,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -547,14 +550,6 @@
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1093,7 +1088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1103,27 +1098,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1138,39 +1124,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1180,20 +1147,44 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1203,6 +1194,130 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1234,47 +1349,50 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1287,10 +1405,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1302,144 +1420,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1760,24 +1750,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46"/>
-      <c r="H1" s="43" t="s">
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="44"/>
+      <c r="H1" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H2" s="70" t="s">
+      <c r="H2" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H3" s="2"/>
@@ -1803,11 +1793,15 @@
       <c r="H5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="2">
+        <v>231</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="32"/>
+      <c r="B6" s="20"/>
       <c r="H6" s="2" t="s">
         <v>49</v>
       </c>
@@ -1816,299 +1810,299 @@
     </row>
     <row r="7" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="121" t="s">
+      <c r="A8" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="120"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="120"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
+      <c r="N8" s="86"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="120"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="86"/>
     </row>
     <row r="10" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="120"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="86"/>
+      <c r="N10" s="86"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="120"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="120"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="120"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="86"/>
+      <c r="N11" s="86"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="120"/>
-      <c r="B12" s="120"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="120"/>
-      <c r="K12" s="120"/>
-      <c r="L12" s="120"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="120"/>
+      <c r="A12" s="86"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="86"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="120"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="120"/>
-      <c r="J13" s="120"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="120"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="M14" s="120"/>
-      <c r="N14" s="120"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="86"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="120"/>
-      <c r="B15" s="120"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="86"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="120"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
+      <c r="A16" s="86"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="120"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="120"/>
+      <c r="A17" s="86"/>
+      <c r="B17" s="86"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="86"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="120"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="120"/>
+      <c r="A18" s="86"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="86"/>
+      <c r="N18" s="86"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="120"/>
-      <c r="B19" s="120"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="120"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="120"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="86"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="120"/>
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="120"/>
-      <c r="L20" s="120"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="120"/>
+      <c r="A20" s="86"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="86"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="120"/>
-      <c r="B21" s="120"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="120"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="120"/>
-      <c r="L21" s="120"/>
-      <c r="M21" s="120"/>
-      <c r="N21" s="120"/>
+      <c r="A21" s="86"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="86"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="86"/>
+      <c r="N21" s="86"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="120"/>
-      <c r="B22" s="120"/>
-      <c r="C22" s="120"/>
-      <c r="D22" s="120"/>
-      <c r="E22" s="120"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="120"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="120"/>
-      <c r="L22" s="120"/>
-      <c r="M22" s="120"/>
-      <c r="N22" s="120"/>
+      <c r="A22" s="86"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="86"/>
+      <c r="N22" s="86"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="120"/>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="120"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="120"/>
-      <c r="N23" s="120"/>
+      <c r="A23" s="86"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="86"/>
+      <c r="N23" s="86"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="120"/>
-      <c r="B24" s="120"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="120"/>
-      <c r="I24" s="120"/>
-      <c r="J24" s="120"/>
-      <c r="K24" s="120"/>
-      <c r="L24" s="120"/>
-      <c r="M24" s="120"/>
-      <c r="N24" s="120"/>
+      <c r="A24" s="86"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="120"/>
-      <c r="B25" s="120"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="120"/>
-      <c r="L25" s="120"/>
-      <c r="M25" s="120"/>
-      <c r="N25" s="120"/>
+      <c r="A25" s="86"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="C26" s="42"/>
+      <c r="C26" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2145,108 +2139,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B3" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="90" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="G5" s="54" t="s">
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="G5" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="65" t="s">
+      <c r="H6" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="63" t="s">
+      <c r="I6" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="67" t="s">
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="67"/>
+      <c r="Q6" s="103"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="87" t="s">
         <v>54</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="19" t="s">
+      <c r="G7" s="96"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="N7" s="63"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="122" t="s">
+      <c r="N7" s="104"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="16" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2254,325 +2248,339 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="47"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="123">
+      <c r="G8" s="32">
         <v>1</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="18">
         <v>101</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="18">
         <v>10</v>
       </c>
-      <c r="L8" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="80"/>
-      <c r="O8" s="81" t="s">
+      <c r="L8" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="99"/>
+      <c r="O8" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q8" s="81"/>
+      <c r="P8" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="100"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="87" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="123">
+      <c r="G9" s="32">
         <v>2</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="18">
+        <v>102</v>
+      </c>
+      <c r="J9" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="30">
-        <v>102</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" s="30">
+      <c r="K9" s="18">
         <v>10</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="80"/>
-      <c r="O9" s="81" t="s">
+      <c r="L9" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="99"/>
+      <c r="O9" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q9" s="81"/>
+      <c r="P9" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9" s="100"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="87"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="123">
+      <c r="G10" s="32">
         <v>3</v>
       </c>
-      <c r="H10" s="124" t="s">
+      <c r="H10" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="18">
         <v>103</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="18">
         <v>10</v>
       </c>
-      <c r="L10" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M10" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="80"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="81"/>
+      <c r="L10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="N10" s="99"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" s="100"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="87" t="s">
         <v>58</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="123">
+      <c r="G11" s="32">
         <v>4</v>
       </c>
-      <c r="H11" s="124" t="s">
+      <c r="H11" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="18">
+        <v>104</v>
+      </c>
+      <c r="J11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="30">
-        <v>104</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" s="30">
+      <c r="K11" s="18">
         <v>8</v>
       </c>
-      <c r="L11" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N11" s="80"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q11" s="81"/>
+      <c r="L11" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" s="99"/>
+      <c r="O11" s="100"/>
+      <c r="P11" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="100"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="47"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="123">
+      <c r="G12" s="32">
         <v>5</v>
       </c>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="80"/>
-      <c r="Q12" s="81"/>
+      <c r="H12" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="18">
+        <v>105</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="18">
+        <v>-5</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M12" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q12" s="100"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="48"/>
+      <c r="C13" s="88"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="G13" s="123">
+      <c r="G13" s="32">
         <v>6</v>
       </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="80"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="80"/>
-      <c r="Q13" s="81"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="100"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="89"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="G14" s="123">
+      <c r="G14" s="32">
         <v>7</v>
       </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="125"/>
-      <c r="O14" s="126"/>
-      <c r="P14" s="80"/>
-      <c r="Q14" s="81"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="97"/>
+      <c r="O14" s="98"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="100"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="47"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="G15" s="123">
+      <c r="G15" s="32">
         <v>8</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="81"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="100"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="100"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="47"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="60"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="111"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="47"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="60"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="111"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="47"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="60"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="108"/>
+      <c r="O18" s="109"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="111"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="G19" s="19"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="60"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="111"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="47"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -2580,8 +2588,8 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -2644,7 +2652,8 @@
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="5.54296875" customWidth="1"/>
     <col min="7" max="7" width="9.453125" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.90625" customWidth="1"/>
+    <col min="9" max="9" width="30.81640625" customWidth="1"/>
     <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.54296875" customWidth="1"/>
     <col min="12" max="12" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -2657,44 +2666,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B3" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="90" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
     </row>
     <row r="6" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
@@ -2706,537 +2715,537 @@
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="G6" s="55" t="s">
+      <c r="E6" s="6"/>
+      <c r="G6" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="65" t="s">
+      <c r="J6" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="78" t="s">
+      <c r="K6" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="78" t="s">
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="120"/>
+      <c r="Q6" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="79"/>
+      <c r="R6" s="120"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="48">
+      <c r="B7" s="88">
         <v>1</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="113" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="106"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B8" s="112"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" s="64"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B8" s="71"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="2" t="s">
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="18">
+        <v>106</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="100"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B9" s="112"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="19">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13" t="s">
+      <c r="G9" s="32">
+        <v>2</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="17">
+        <v>107</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="N9" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="122"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B10" s="112"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="12" t="s">
+      <c r="J10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="17">
+        <v>108</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="18">
+        <v>10</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="O10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="30">
-        <v>101</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="M8" s="30">
-        <v>0</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="P10" s="18"/>
+      <c r="Q10" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" s="100"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B11" s="112"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="2"/>
+      <c r="G11" s="14">
+        <v>4</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="80" t="s">
+      <c r="J11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="17">
+        <v>109</v>
+      </c>
+      <c r="L11" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="R8" s="81"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B9" s="71"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="123">
+      <c r="M11" s="18">
+        <v>10</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="R11" s="100"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B12" s="89"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="2"/>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="100"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B13" s="88">
         <v>2</v>
       </c>
-      <c r="H9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="29">
-        <v>102</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="30">
-        <v>0.01</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="127" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9" s="58"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B10" s="71"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="2" t="s">
+      <c r="C13" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G13" s="32">
+        <v>6</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="122"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B14" s="112"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="100"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B15" s="112"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="100"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B16" s="112"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="14">
+        <v>9</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="100"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B17" s="112"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="2"/>
+      <c r="G17" s="14">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="100"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="2"/>
+      <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="8"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="100"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B19" s="88">
         <v>3</v>
       </c>
-      <c r="H10" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="29">
-        <v>103</v>
-      </c>
-      <c r="L10" s="30" t="s">
+      <c r="C19" s="113"/>
+      <c r="D19" s="2"/>
+      <c r="G19" s="14">
         <v>12</v>
       </c>
-      <c r="M10" s="30">
-        <v>10</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="O10" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="R10" s="81"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B11" s="71"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="2"/>
-      <c r="G11" s="19">
+      <c r="H19" s="8"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="100"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B20" s="112"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="2"/>
+      <c r="G20" s="14">
+        <v>13</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="99"/>
+      <c r="R20" s="100"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B21" s="112"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="2"/>
+      <c r="G21" s="14">
+        <v>14</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="99"/>
+      <c r="R21" s="100"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B22" s="112"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="2"/>
+      <c r="G22" s="14">
+        <v>15</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="100"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B23" s="112"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="2"/>
+      <c r="G23" s="14">
+        <v>16</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="99"/>
+      <c r="R23" s="100"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B24" s="89"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="2"/>
+      <c r="G24" s="14">
+        <v>17</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="100"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B25" s="88">
         <v>4</v>
       </c>
-      <c r="H11" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="29">
-        <v>104</v>
-      </c>
-      <c r="L11" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="M11" s="30">
-        <v>10</v>
-      </c>
-      <c r="N11" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="R11" s="81"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B12" s="49"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="2"/>
-      <c r="G12" s="19">
-        <v>5</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="80"/>
-      <c r="R12" s="81"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B13" s="48">
-        <v>2</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="123">
-        <v>6</v>
-      </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="57"/>
-      <c r="R13" s="58"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="19">
-        <v>7</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="80"/>
-      <c r="R14" s="81"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="19">
-        <v>8</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="81"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="19">
-        <v>9</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="80"/>
-      <c r="R16" s="81"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="2"/>
-      <c r="G17" s="19">
-        <v>10</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="80"/>
-      <c r="R17" s="81"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="2"/>
-      <c r="G18" s="19">
-        <v>11</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="81"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B19" s="48">
-        <v>3</v>
-      </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="2"/>
-      <c r="G19" s="19">
-        <v>12</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="80"/>
-      <c r="R19" s="81"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B20" s="71"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="2"/>
-      <c r="G20" s="19">
-        <v>13</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="80"/>
-      <c r="R20" s="81"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B21" s="71"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="2"/>
-      <c r="G21" s="19">
-        <v>14</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="81"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B22" s="71"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="2"/>
-      <c r="G22" s="19">
-        <v>15</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B23" s="71"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="2"/>
-      <c r="G23" s="19">
-        <v>16</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="81"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B24" s="49"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="2"/>
-      <c r="G24" s="19">
-        <v>17</v>
-      </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="80"/>
-      <c r="R24" s="81"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B25" s="48">
-        <v>4</v>
-      </c>
-      <c r="C25" s="72"/>
+      <c r="C25" s="113"/>
       <c r="D25" s="2"/>
-      <c r="G25" s="19">
+      <c r="G25" s="14">
         <v>18</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="80"/>
-      <c r="R25" s="81"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="100"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B26" s="71"/>
-      <c r="C26" s="73"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="114"/>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B27" s="71"/>
-      <c r="C27" s="73"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="114"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B28" s="71"/>
-      <c r="C28" s="73"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="114"/>
       <c r="D28" s="2"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="38"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="107"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="26"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B29" s="71"/>
-      <c r="C29" s="73"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="114"/>
       <c r="D29" s="2"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="75"/>
-      <c r="M29" s="75"/>
-      <c r="N29" s="39"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="116"/>
+      <c r="N29" s="27"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B30" s="49"/>
-      <c r="C30" s="74"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="115"/>
       <c r="D30" s="2"/>
     </row>
   </sheetData>
@@ -3307,407 +3316,523 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="63" t="s">
+      <c r="F4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="67" t="s">
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="67"/>
+      <c r="N4" s="47"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="100"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="22" t="s">
+      <c r="B5" s="64"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="85"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="22" t="s">
+      <c r="K5" s="45"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="36" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="20">
+      <c r="B6" s="38">
         <v>1</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="25">
+      <c r="E6" s="38"/>
+      <c r="F6" s="40">
         <v>101</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="40">
         <v>10</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="48"/>
+      <c r="L6" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="87"/>
-      <c r="L6" s="88" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>66</v>
+      <c r="N6" s="38" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="10">
+      <c r="B7" s="32">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="27"/>
-      <c r="E7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="9">
-        <v>102</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="C7" s="61"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="34">
+        <v>106</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="34">
+        <v>0</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="50"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="89"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>89</v>
+      <c r="N7" s="32" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="10">
+      <c r="B8" s="32">
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="10"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="34">
+        <v>102</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="34">
+        <v>10</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="10">
+      <c r="B9" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="32">
+        <v>107</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="52"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="32" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="10">
+      <c r="B10" s="32">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="10"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="41">
+        <v>103</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="34">
+        <v>10</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="50"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B11" s="10">
+      <c r="B11" s="32">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="10"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="41">
+        <v>108</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="34">
+        <v>10</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="50"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="N11" s="32" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="10">
+      <c r="B12" s="32">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="98"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="10"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="41">
+        <v>104</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="34">
+        <v>8</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="50"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="21">
+      <c r="B13" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="36">
+        <v>109</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="36">
+        <v>10</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="45"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
     </row>
     <row r="15" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="97"/>
-      <c r="M15" s="7"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="5"/>
     </row>
     <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M16" s="7"/>
+      <c r="M16" s="5"/>
     </row>
     <row r="17" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="109" t="s">
+      <c r="C17" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="111"/>
-      <c r="G17" s="34" t="s">
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="109" t="s">
+      <c r="H17" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="112"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="109" t="s">
+      <c r="I17" s="76"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="74"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="N17" s="112"/>
-      <c r="O17" s="110"/>
-      <c r="P17" s="111"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="75"/>
     </row>
     <row r="18" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="107" t="s">
+      <c r="D18" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="107" t="s">
+      <c r="E18" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="108" t="s">
+      <c r="F18" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="117" t="s">
+      <c r="G18" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="113" t="s">
+      <c r="H18" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="114"/>
-      <c r="J18" s="107" t="s">
+      <c r="I18" s="78"/>
+      <c r="J18" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="107" t="s">
+      <c r="K18" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="108" t="s">
+      <c r="L18" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="M18" s="118" t="s">
+      <c r="M18" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="107" t="s">
+      <c r="N18" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="O18" s="107" t="s">
+      <c r="O18" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="P18" s="108" t="s">
+      <c r="P18" s="72" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B19" s="105"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="119"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="108"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="40"/>
+      <c r="C20" s="21">
+        <v>8</v>
+      </c>
+      <c r="D20" s="23">
+        <v>8</v>
+      </c>
+      <c r="E20" s="23">
+        <v>0</v>
+      </c>
+      <c r="F20" s="24">
+        <v>0</v>
+      </c>
+      <c r="G20" s="29">
+        <v>0</v>
+      </c>
+      <c r="H20" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="68"/>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="23">
+        <v>0</v>
+      </c>
+      <c r="L20" s="24">
+        <v>0</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>83</v>
+      </c>
       <c r="N20" s="2">
-        <v>5</v>
-      </c>
-      <c r="O20" s="35">
-        <v>5</v>
-      </c>
-      <c r="P20" s="36">
+        <v>8</v>
+      </c>
+      <c r="O20" s="23">
+        <v>8</v>
+      </c>
+      <c r="P20" s="24">
         <v>0</v>
       </c>
     </row>
@@ -3760,6 +3885,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3768,7 +3899,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23dedcede4fc4caec29d0314c04f027b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -3882,13 +4013,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3896,7 +4030,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9531F88B-55A0-44BD-B315-36208334B717}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3910,13 +4044,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06259BE4-5400-4C55-BB30-36C11C515CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB692758-FFC0-49A0-9472-DA4EFB7584E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>Autor</author>
   </authors>
   <commentList>
     <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
@@ -46,7 +46,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
+          <t>Autor:</t>
         </r>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>Autor</author>
   </authors>
   <commentList>
     <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
@@ -81,7 +81,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
+          <t>Autor:</t>
         </r>
         <r>
           <rPr>
@@ -105,7 +105,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
+          <t>Autor:</t>
         </r>
         <r>
           <rPr>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="98">
   <si>
     <t>Condition</t>
   </si>
@@ -434,9 +434,6 @@
     <t>TC_BVA_Valid_Add_Product</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>"Sprite"</t>
   </si>
   <si>
@@ -465,6 +462,12 @@
   </si>
   <si>
     <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1185,6 +1188,78 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1239,78 +1314,6 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1318,6 +1321,45 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1354,43 +1396,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1407,30 +1434,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1750,12 +1753,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="44"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
       <c r="H1" s="31" t="s">
         <v>38</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" s="2">
         <v>231</v>
@@ -2139,43 +2142,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="44"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="105"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B5" s="93" t="s">
+      <c r="B5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="G5" s="94" t="s">
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="G5" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="107"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" s="14" t="s">
@@ -2190,39 +2193,39 @@
       <c r="E6" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="101" t="s">
+      <c r="H6" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="105"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="103" t="s">
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="103"/>
+      <c r="Q6" s="96"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="100" t="s">
         <v>54</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="102"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="95"/>
       <c r="I7" s="14" t="s">
         <v>60</v>
       </c>
@@ -2238,8 +2241,8 @@
       <c r="M7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="N7" s="104"/>
-      <c r="O7" s="106"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="99"/>
       <c r="P7" s="16" t="s">
         <v>10</v>
       </c>
@@ -2248,7 +2251,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="87"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>55</v>
@@ -2269,25 +2272,25 @@
         <v>10</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="N8" s="99"/>
-      <c r="O8" s="100" t="s">
+      <c r="N8" s="88"/>
+      <c r="O8" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="99" t="s">
+      <c r="P8" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="Q8" s="100"/>
+      <c r="Q8" s="89"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="100" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -2310,25 +2313,25 @@
         <v>10</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="99"/>
-      <c r="O9" s="100" t="s">
+      <c r="N9" s="88"/>
+      <c r="O9" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q9" s="100"/>
+      <c r="P9" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="89"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="87"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>57</v>
@@ -2349,23 +2352,23 @@
         <v>10</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="99"/>
-      <c r="O10" s="100"/>
-      <c r="P10" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="100"/>
+      <c r="N10" s="88"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="89"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="87" t="s">
+      <c r="C11" s="100" t="s">
         <v>58</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -2388,23 +2391,23 @@
         <v>8</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M11" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="N11" s="99"/>
-      <c r="O11" s="100"/>
-      <c r="P11" s="99" t="s">
+      <c r="N11" s="88"/>
+      <c r="O11" s="89"/>
+      <c r="P11" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="Q11" s="100"/>
+      <c r="Q11" s="89"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="87"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>59</v>
@@ -2413,35 +2416,35 @@
         <v>5</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" s="18">
         <v>105</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K12" s="18">
         <v>-5</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M12" s="18" t="s">
         <v>84</v>
       </c>
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
-      <c r="P12" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q12" s="100"/>
+      <c r="P12" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q12" s="89"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="88"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="G13" s="32">
@@ -2453,16 +2456,16 @@
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="100"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="89"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="89"/>
+      <c r="C14" s="102"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="G14" s="32">
@@ -2474,16 +2477,16 @@
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
-      <c r="N14" s="97"/>
-      <c r="O14" s="98"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="100"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="89"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="87"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="G15" s="32">
@@ -2495,16 +2498,16 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="100"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="100"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="89"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="87"/>
+      <c r="C16" s="100"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="10"/>
@@ -2514,16 +2517,16 @@
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="111"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="93"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="87"/>
+      <c r="C17" s="100"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="G17" s="10"/>
@@ -2533,16 +2536,16 @@
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
-      <c r="N17" s="108"/>
-      <c r="O17" s="109"/>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="111"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="93"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="87"/>
+      <c r="C18" s="100"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="10"/>
@@ -2552,16 +2555,16 @@
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="109"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="111"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="87"/>
+      <c r="C19" s="100"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="G19" s="14"/>
@@ -2571,16 +2574,16 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="109"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="111"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="93"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="87"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -2588,35 +2591,11 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -2633,6 +2612,30 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2666,22 +2669,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="44"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="105"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B5" s="118" t="s">
@@ -2690,20 +2693,20 @@
       <c r="C5" s="118"/>
       <c r="D5" s="118"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="94" t="s">
+      <c r="G5" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="107"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="107"/>
     </row>
     <row r="6" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
@@ -2716,45 +2719,45 @@
         <v>13</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="95" t="s">
+      <c r="H6" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="95" t="s">
+      <c r="I6" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="101" t="s">
+      <c r="J6" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="119" t="s">
+      <c r="K6" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="124"/>
-      <c r="O6" s="124"/>
-      <c r="P6" s="120"/>
-      <c r="Q6" s="119" t="s">
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="116"/>
+      <c r="Q6" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="120"/>
+      <c r="R6" s="116"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="88">
+      <c r="B7" s="101">
         <v>1</v>
       </c>
-      <c r="C7" s="113" t="s">
+      <c r="C7" s="121" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="102"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="95"/>
       <c r="K7" s="14" t="s">
         <v>60</v>
       </c>
@@ -2771,14 +2774,14 @@
         <v>63</v>
       </c>
       <c r="P7" s="14"/>
-      <c r="Q7" s="104" t="s">
+      <c r="Q7" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="R7" s="106"/>
+      <c r="R7" s="99"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B8" s="112"/>
-      <c r="C8" s="114"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="122"/>
       <c r="D8" s="2" t="s">
         <v>74</v>
       </c>
@@ -2804,20 +2807,20 @@
         <v>0</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O8" s="18" t="s">
         <v>84</v>
       </c>
       <c r="P8" s="18"/>
-      <c r="Q8" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="100"/>
+      <c r="Q8" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="89"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B9" s="112"/>
-      <c r="C9" s="114"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="122"/>
       <c r="D9" s="2" t="s">
         <v>75</v>
       </c>
@@ -2831,32 +2834,32 @@
         <v>85</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K9" s="17">
         <v>107</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M9" s="18">
         <v>0.01</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O9" s="18" t="s">
         <v>84</v>
       </c>
       <c r="P9" s="18"/>
-      <c r="Q9" s="121" t="s">
+      <c r="Q9" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="R9" s="122"/>
+      <c r="R9" s="113"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B10" s="112"/>
-      <c r="C10" s="114"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="122"/>
       <c r="D10" s="2" t="s">
         <v>76</v>
       </c>
@@ -2870,7 +2873,7 @@
         <v>82</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K10" s="17">
         <v>108</v>
@@ -2882,20 +2885,20 @@
         <v>10</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O10" s="18" t="s">
         <v>84</v>
       </c>
       <c r="P10" s="18"/>
-      <c r="Q10" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="R10" s="100"/>
+      <c r="Q10" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="89"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B11" s="112"/>
-      <c r="C11" s="114"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="122"/>
       <c r="D11" s="2"/>
       <c r="G11" s="14">
         <v>4</v>
@@ -2907,32 +2910,32 @@
         <v>85</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K11" s="17">
         <v>109</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M11" s="18">
         <v>10</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O11" s="18" t="s">
         <v>84</v>
       </c>
       <c r="P11" s="18"/>
-      <c r="Q11" s="99" t="s">
+      <c r="Q11" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="R11" s="100"/>
+      <c r="R11" s="89"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B12" s="89"/>
-      <c r="C12" s="115"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="123"/>
       <c r="D12" s="2"/>
       <c r="G12" s="14">
         <v>5</v>
@@ -2946,14 +2949,14 @@
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
       <c r="P12" s="18"/>
-      <c r="Q12" s="99"/>
-      <c r="R12" s="100"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="89"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B13" s="88">
+      <c r="B13" s="101">
         <v>2</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="101" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="32">
@@ -2968,12 +2971,12 @@
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="122"/>
+      <c r="Q13" s="112"/>
+      <c r="R13" s="113"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B14" s="112"/>
-      <c r="C14" s="112"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="120"/>
       <c r="D14" s="2" t="s">
         <v>78</v>
       </c>
@@ -2989,12 +2992,12 @@
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
       <c r="P14" s="18"/>
-      <c r="Q14" s="99"/>
-      <c r="R14" s="100"/>
+      <c r="Q14" s="88"/>
+      <c r="R14" s="89"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B15" s="112"/>
-      <c r="C15" s="112"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
       <c r="D15" s="2" t="s">
         <v>79</v>
       </c>
@@ -3010,12 +3013,12 @@
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
       <c r="P15" s="18"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="100"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="89"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B16" s="112"/>
-      <c r="C16" s="112"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
       <c r="D16" s="2" t="s">
         <v>80</v>
       </c>
@@ -3031,12 +3034,12 @@
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="100"/>
+      <c r="Q16" s="88"/>
+      <c r="R16" s="89"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="120"/>
       <c r="D17" s="2"/>
       <c r="G17" s="14">
         <v>10</v>
@@ -3050,12 +3053,12 @@
       <c r="N17" s="18"/>
       <c r="O17" s="18"/>
       <c r="P17" s="18"/>
-      <c r="Q17" s="99"/>
-      <c r="R17" s="100"/>
+      <c r="Q17" s="88"/>
+      <c r="R17" s="89"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
       <c r="D18" s="2"/>
       <c r="G18" s="14">
         <v>11</v>
@@ -3069,14 +3072,14 @@
       <c r="N18" s="18"/>
       <c r="O18" s="18"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="99"/>
-      <c r="R18" s="100"/>
+      <c r="Q18" s="88"/>
+      <c r="R18" s="89"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B19" s="88">
+      <c r="B19" s="101">
         <v>3</v>
       </c>
-      <c r="C19" s="113"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="2"/>
       <c r="G19" s="14">
         <v>12</v>
@@ -3090,12 +3093,12 @@
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="100"/>
+      <c r="Q19" s="88"/>
+      <c r="R19" s="89"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B20" s="112"/>
-      <c r="C20" s="114"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="122"/>
       <c r="D20" s="2"/>
       <c r="G20" s="14">
         <v>13</v>
@@ -3109,12 +3112,12 @@
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
       <c r="P20" s="18"/>
-      <c r="Q20" s="99"/>
-      <c r="R20" s="100"/>
+      <c r="Q20" s="88"/>
+      <c r="R20" s="89"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B21" s="112"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="122"/>
       <c r="D21" s="2"/>
       <c r="G21" s="14">
         <v>14</v>
@@ -3128,12 +3131,12 @@
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="99"/>
-      <c r="R21" s="100"/>
+      <c r="Q21" s="88"/>
+      <c r="R21" s="89"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B22" s="112"/>
-      <c r="C22" s="114"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="122"/>
       <c r="D22" s="2"/>
       <c r="G22" s="14">
         <v>15</v>
@@ -3147,12 +3150,12 @@
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
       <c r="P22" s="18"/>
-      <c r="Q22" s="99"/>
-      <c r="R22" s="100"/>
+      <c r="Q22" s="88"/>
+      <c r="R22" s="89"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B23" s="112"/>
-      <c r="C23" s="114"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="2"/>
       <c r="G23" s="14">
         <v>16</v>
@@ -3166,12 +3169,12 @@
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
       <c r="P23" s="18"/>
-      <c r="Q23" s="99"/>
-      <c r="R23" s="100"/>
+      <c r="Q23" s="88"/>
+      <c r="R23" s="89"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B24" s="89"/>
-      <c r="C24" s="115"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="123"/>
       <c r="D24" s="2"/>
       <c r="G24" s="14">
         <v>17</v>
@@ -3185,14 +3188,14 @@
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
       <c r="P24" s="18"/>
-      <c r="Q24" s="99"/>
-      <c r="R24" s="100"/>
+      <c r="Q24" s="88"/>
+      <c r="R24" s="89"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B25" s="88">
+      <c r="B25" s="101">
         <v>4</v>
       </c>
-      <c r="C25" s="113"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="2"/>
       <c r="G25" s="14">
         <v>18</v>
@@ -3206,25 +3209,25 @@
       <c r="N25" s="18"/>
       <c r="O25" s="18"/>
       <c r="P25" s="18"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="100"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="89"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B26" s="112"/>
-      <c r="C26" s="114"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B27" s="112"/>
-      <c r="C27" s="114"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="122"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B28" s="112"/>
-      <c r="C28" s="114"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="122"/>
       <c r="D28" s="2"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="107"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
       <c r="I28" s="117"/>
       <c r="J28" s="117"/>
       <c r="K28" s="117"/>
@@ -3233,31 +3236,39 @@
       <c r="N28" s="26"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B29" s="112"/>
-      <c r="C29" s="114"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="122"/>
       <c r="D29" s="2"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
+      <c r="I29" s="124"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="124"/>
+      <c r="L29" s="124"/>
+      <c r="M29" s="124"/>
       <c r="N29" s="27"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B30" s="89"/>
-      <c r="C30" s="115"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="123"/>
       <c r="D30" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
@@ -3274,22 +3285,14 @@
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:R5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3316,62 +3319,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="44"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="47" t="s">
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="47"/>
+      <c r="N4" s="71"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="64"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="56"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="80"/>
       <c r="F5" s="36" t="s">
         <v>60</v>
       </c>
@@ -3387,8 +3390,8 @@
       <c r="J5" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="46"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="70"/>
       <c r="M5" s="36" t="s">
         <v>10</v>
       </c>
@@ -3400,7 +3403,7 @@
       <c r="B6" s="38">
         <v>1</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="51" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="39" t="s">
@@ -3417,13 +3420,13 @@
         <v>10</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J6" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="48"/>
-      <c r="L6" s="49" t="s">
+      <c r="K6" s="72"/>
+      <c r="L6" s="73" t="s">
         <v>7</v>
       </c>
       <c r="M6" s="40" t="s">
@@ -3438,10 +3441,10 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="61"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="35"/>
       <c r="E7" s="33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="34">
         <v>106</v>
@@ -3453,18 +3456,18 @@
         <v>0</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J7" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="50"/>
-      <c r="L7" s="51"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="75"/>
       <c r="M7" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
@@ -3472,7 +3475,7 @@
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="61"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="35" t="s">
         <v>66</v>
       </c>
@@ -3487,7 +3490,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J8" s="34" t="s">
         <v>84</v>
@@ -3495,10 +3498,10 @@
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
       <c r="M8" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
@@ -3506,28 +3509,28 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="61"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="35"/>
       <c r="E9" s="32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="32">
         <v>107</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="32">
         <v>0.01</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J9" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="52"/>
-      <c r="L9" s="54"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="78"/>
       <c r="M9" s="32" t="s">
         <v>65</v>
       </c>
@@ -3540,7 +3543,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="61"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="35" t="s">
         <v>41</v>
       </c>
@@ -3555,18 +3558,18 @@
         <v>10</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J10" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="75"/>
       <c r="M10" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
@@ -3574,10 +3577,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="61"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="35"/>
       <c r="E11" s="32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" s="41">
         <v>108</v>
@@ -3589,18 +3592,18 @@
         <v>10</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J11" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="50"/>
-      <c r="L11" s="51"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="75"/>
       <c r="M11" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
@@ -3608,7 +3611,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="61"/>
+      <c r="C12" s="51"/>
       <c r="D12" s="35" t="s">
         <v>68</v>
       </c>
@@ -3623,13 +3626,13 @@
         <v>8</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J12" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="75"/>
       <c r="M12" s="34" t="s">
         <v>65</v>
       </c>
@@ -3642,28 +3645,28 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="62"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="37"/>
       <c r="E13" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="36">
         <v>109</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H13" s="36">
         <v>10</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J13" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="45"/>
-      <c r="L13" s="46"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="70"/>
       <c r="M13" s="36" t="s">
         <v>65</v>
       </c>
@@ -3698,98 +3701,98 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="73" t="s">
+      <c r="C17" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="75"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
       <c r="G17" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="73" t="s">
+      <c r="H17" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="76"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="75"/>
-      <c r="M17" s="73" t="s">
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="N17" s="76"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="75"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
     </row>
     <row r="18" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="81" t="s">
+      <c r="G18" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="77" t="s">
+      <c r="H18" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="78"/>
-      <c r="J18" s="71" t="s">
+      <c r="I18" s="62"/>
+      <c r="J18" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="71" t="s">
+      <c r="K18" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="72" t="s">
+      <c r="L18" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="M18" s="82" t="s">
+      <c r="M18" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="71" t="s">
+      <c r="N18" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="O18" s="71" t="s">
+      <c r="O18" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="P18" s="72" t="s">
+      <c r="P18" s="42" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B19" s="69"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="72"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="42"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="25" t="s">
@@ -3810,27 +3813,27 @@
       <c r="G20" s="29">
         <v>0</v>
       </c>
-      <c r="H20" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" s="68"/>
+      <c r="H20" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="I20" s="58"/>
       <c r="J20" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K20" s="23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L20" s="24">
         <v>0</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="N20" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" s="23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P20" s="24">
         <v>0</v>
@@ -3841,12 +3844,20 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
@@ -3863,20 +3874,12 @@
     <mergeCell ref="H18:I19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="K18:K19"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3885,21 +3888,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23dedcede4fc4caec29d0314c04f027b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -4013,10 +4001,32 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9531F88B-55A0-44BD-B315-36208334B717}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
@@ -4031,16 +4041,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9531F88B-55A0-44BD-B315-36208334B717}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
